--- a/SuppXLS/Scen_UC_CO2BND_CNDC.xlsx
+++ b/SuppXLS/Scen_UC_CO2BND_CNDC.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\My Drive\001_Academic\002_Course_Works\003_2026_Sping_Semester\003_Low-Carbon Technologies and Policies\000_ICP_BL\006_Cambodia_TIMES_Model_V002\KHM_TIMES_V002_20260605\SuppXLS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261025_v01\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8752AA18-CC18-42A6-AF25-8CC094A75413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B639C1-BD97-400E-9F97-DF88ADF3B238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UC_CO2" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
   <si>
     <t>~UC_Sets: R_E: AllRegions</t>
   </si>
@@ -74,9 +87,6 @@
   </si>
   <si>
     <t>UC_COMNET</t>
-  </si>
-  <si>
-    <t>UC_RHSRTS~0</t>
   </si>
   <si>
     <t>~UC_T:UC_RHSRTS</t>
@@ -131,7 +141,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -180,11 +193,20 @@
       <sz val="8.25"/>
       <color rgb="FF2B2C3C"/>
       <name val="Microsoft Sans Serif"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8.25"/>
       <color rgb="FF000000"/>
       <name val="Microsoft Sans Serif"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="10">
@@ -267,10 +289,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -280,7 +303,6 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -305,8 +327,10 @@
     <xf numFmtId="49" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
+    <cellStyle name="Comma" xfId="3" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 10" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normale_Scen_UC_IND-StrucConst" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
@@ -798,45 +822,44 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R35"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.109375" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" customWidth="1"/>
-    <col min="4" max="4" width="30.109375" customWidth="1"/>
-    <col min="5" max="6" width="11.109375" customWidth="1"/>
-    <col min="7" max="7" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="11.109375" customWidth="1"/>
-    <col min="10" max="10" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.88671875" customWidth="1"/>
+    <col min="2" max="2" width="14.140625" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" customWidth="1"/>
+    <col min="4" max="4" width="30.140625" customWidth="1"/>
+    <col min="5" max="6" width="11.140625" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="11.140625" customWidth="1"/>
+    <col min="10" max="10" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="15" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B3" s="6" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="J4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>1</v>
       </c>
@@ -867,25 +890,22 @@
       <c r="K5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="L5" s="9" t="s">
+      <c r="L5" s="8" t="s">
         <v>13</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>18</v>
       </c>
       <c r="N5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="R5" s="10" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="R5" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="G6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I6">
         <v>2030</v>
@@ -896,22 +916,19 @@
       <c r="K6">
         <v>1</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="17">
         <v>32850.09812767776</v>
-      </c>
-      <c r="M6">
-        <v>5</v>
       </c>
       <c r="N6" t="s">
         <v>16</v>
       </c>
-      <c r="R6" s="11">
+      <c r="R6" s="10">
         <v>0.95</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="G7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I7">
         <v>2035</v>
@@ -922,298 +939,298 @@
       <c r="K7">
         <v>1</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="17">
         <v>29390.040974058222</v>
       </c>
-      <c r="R7" s="11">
+      <c r="R7" s="10">
         <v>0.95</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="R8" s="11">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R8" s="10">
         <v>0.95</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="R9" s="11">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R9" s="10">
         <v>0.95</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="L10" s="8"/>
-      <c r="R10" s="11">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="L10" s="7"/>
+      <c r="R10" s="10">
         <v>0.95</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="L11" s="8"/>
-      <c r="R11" s="11">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="L11" s="7"/>
+      <c r="R11" s="10">
         <v>0.95</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="L12" s="8"/>
-      <c r="R12" s="11">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="L12" s="7"/>
+      <c r="R12" s="10">
         <v>0.95</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="L13" s="8"/>
-      <c r="R13" s="11"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="R14" s="11"/>
-    </row>
-    <row r="24" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="D24" s="12" t="s">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="L13" s="7"/>
+      <c r="R13" s="10"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="R14" s="10"/>
+    </row>
+    <row r="24" spans="4:13" x14ac:dyDescent="0.25">
+      <c r="D24" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="E24" s="12" t="s">
+      <c r="F24" s="12">
+        <v>2021</v>
+      </c>
+      <c r="G24" s="12">
+        <v>2022</v>
+      </c>
+      <c r="H24" s="12">
+        <v>2025</v>
+      </c>
+      <c r="I24" s="12">
+        <v>2030</v>
+      </c>
+      <c r="J24" s="12">
+        <v>2035</v>
+      </c>
+      <c r="K24" s="12">
+        <v>2040</v>
+      </c>
+      <c r="L24" s="12">
+        <v>2045</v>
+      </c>
+      <c r="M24" s="12">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="25" spans="4:13" x14ac:dyDescent="0.25">
+      <c r="D25" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="F24" s="13">
-        <v>2021</v>
-      </c>
-      <c r="G24" s="13">
-        <v>2022</v>
-      </c>
-      <c r="H24" s="13">
-        <v>2025</v>
-      </c>
-      <c r="I24" s="13">
-        <v>2030</v>
-      </c>
-      <c r="J24" s="13">
-        <v>2035</v>
-      </c>
-      <c r="K24" s="13">
-        <v>2040</v>
-      </c>
-      <c r="L24" s="13">
-        <v>2045</v>
-      </c>
-      <c r="M24" s="13">
-        <v>2050</v>
-      </c>
-    </row>
-    <row r="25" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="D25" s="14" t="s">
+      <c r="E25" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="E25" s="14" t="s">
+      <c r="F25" s="14">
+        <v>693.95486520960105</v>
+      </c>
+      <c r="G25" s="14">
+        <v>850.67300560276703</v>
+      </c>
+      <c r="H25" s="14">
+        <v>1347.2678506698301</v>
+      </c>
+      <c r="I25" s="14">
+        <v>2177.8569201731798</v>
+      </c>
+      <c r="J25" s="14">
+        <v>3086.7378682377598</v>
+      </c>
+      <c r="K25" s="14">
+        <v>3714.0025192061698</v>
+      </c>
+      <c r="L25" s="14">
+        <v>4301.5419160375204</v>
+      </c>
+      <c r="M25" s="14">
+        <v>4964.56021902459</v>
+      </c>
+    </row>
+    <row r="26" spans="4:13" x14ac:dyDescent="0.25">
+      <c r="D26" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="F25" s="15">
-        <v>693.95486520960105</v>
-      </c>
-      <c r="G25" s="15">
-        <v>850.67300560276703</v>
-      </c>
-      <c r="H25" s="15">
-        <v>1347.2678506698301</v>
-      </c>
-      <c r="I25" s="15">
-        <v>2177.8569201731798</v>
-      </c>
-      <c r="J25" s="15">
-        <v>3086.7378682377598</v>
-      </c>
-      <c r="K25" s="15">
-        <v>3714.0025192061698</v>
-      </c>
-      <c r="L25" s="15">
-        <v>4301.5419160375204</v>
-      </c>
-      <c r="M25" s="15">
-        <v>4964.56021902459</v>
-      </c>
-    </row>
-    <row r="26" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="D26" s="14" t="s">
+      <c r="E26" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F26" s="14">
+        <v>415.09356099436798</v>
+      </c>
+      <c r="G26" s="14">
+        <v>617.52024838757598</v>
+      </c>
+      <c r="H26" s="15"/>
+      <c r="I26" s="15"/>
+      <c r="J26" s="15"/>
+      <c r="K26" s="15"/>
+      <c r="L26" s="15"/>
+      <c r="M26" s="15"/>
+    </row>
+    <row r="27" spans="4:13" x14ac:dyDescent="0.25">
+      <c r="D27" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E26" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="F26" s="15">
-        <v>415.09356099436798</v>
-      </c>
-      <c r="G26" s="15">
-        <v>617.52024838757598</v>
-      </c>
-      <c r="H26" s="16"/>
-      <c r="I26" s="16"/>
-      <c r="J26" s="16"/>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-    </row>
-    <row r="27" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="D27" s="14" t="s">
+      <c r="E27" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F27" s="14">
+        <v>4320.3443550000002</v>
+      </c>
+      <c r="G27" s="14">
+        <v>4176.0923665500004</v>
+      </c>
+      <c r="H27" s="14">
+        <v>9631.1882730587695</v>
+      </c>
+      <c r="I27" s="14">
+        <v>12572.914697550001</v>
+      </c>
+      <c r="J27" s="14">
+        <v>15672.6971842121</v>
+      </c>
+      <c r="K27" s="14">
+        <v>18560.776887263</v>
+      </c>
+      <c r="L27" s="14">
+        <v>21899.462424407098</v>
+      </c>
+      <c r="M27" s="14">
+        <v>27838.400788229799</v>
+      </c>
+    </row>
+    <row r="28" spans="4:13" x14ac:dyDescent="0.25">
+      <c r="D28" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="E27" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="F27" s="15">
-        <v>4320.3443550000002</v>
-      </c>
-      <c r="G27" s="15">
-        <v>4176.0923665500004</v>
-      </c>
-      <c r="H27" s="15">
-        <v>9631.1882730587695</v>
-      </c>
-      <c r="I27" s="15">
-        <v>12572.914697550001</v>
-      </c>
-      <c r="J27" s="15">
-        <v>15672.6971842121</v>
-      </c>
-      <c r="K27" s="15">
-        <v>18560.776887263</v>
-      </c>
-      <c r="L27" s="15">
-        <v>21899.462424407098</v>
-      </c>
-      <c r="M27" s="15">
-        <v>27838.400788229799</v>
-      </c>
-    </row>
-    <row r="28" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="D28" s="14" t="s">
+      <c r="E28" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F28" s="14">
+        <v>11150.4292166014</v>
+      </c>
+      <c r="G28" s="14">
+        <v>11169.466907087801</v>
+      </c>
+      <c r="H28" s="14">
+        <v>10997.569262306601</v>
+      </c>
+      <c r="I28" s="14">
+        <v>10711.1201093421</v>
+      </c>
+      <c r="J28" s="14">
+        <v>10424.7297356621</v>
+      </c>
+      <c r="K28" s="14">
+        <v>10138.398288361899</v>
+      </c>
+      <c r="L28" s="14">
+        <v>9852.1259149048492</v>
+      </c>
+      <c r="M28" s="14">
+        <v>9565.9127631232695</v>
+      </c>
+    </row>
+    <row r="29" spans="4:13" x14ac:dyDescent="0.25">
+      <c r="D29" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="E28" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="F28" s="15">
-        <v>11150.4292166014</v>
-      </c>
-      <c r="G28" s="15">
-        <v>11169.466907087801</v>
-      </c>
-      <c r="H28" s="15">
-        <v>10997.569262306601</v>
-      </c>
-      <c r="I28" s="15">
-        <v>10711.1201093421</v>
-      </c>
-      <c r="J28" s="15">
-        <v>10424.7297356621</v>
-      </c>
-      <c r="K28" s="15">
-        <v>10138.398288361899</v>
-      </c>
-      <c r="L28" s="15">
-        <v>9852.1259149048492</v>
-      </c>
-      <c r="M28" s="15">
-        <v>9565.9127631232695</v>
-      </c>
-    </row>
-    <row r="29" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="D29" s="14" t="s">
+      <c r="E29" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F29" s="14">
+        <v>4026.4255253246401</v>
+      </c>
+      <c r="G29" s="14">
+        <v>4913.2020396430598</v>
+      </c>
+      <c r="H29" s="14">
+        <v>5687.6455111417899</v>
+      </c>
+      <c r="I29" s="14">
+        <v>7259.0370999061797</v>
+      </c>
+      <c r="J29" s="14">
+        <v>9264.5752121137193</v>
+      </c>
+      <c r="K29" s="14">
+        <v>11824.206527615201</v>
+      </c>
+      <c r="L29" s="14">
+        <v>15091.0167823875</v>
+      </c>
+      <c r="M29" s="14">
+        <v>18355.616359657</v>
+      </c>
+    </row>
+    <row r="30" spans="4:13" x14ac:dyDescent="0.25">
+      <c r="D30" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F30" s="14">
+        <v>6668.8297496027999</v>
+      </c>
+      <c r="G30" s="14">
+        <v>3770.2856351884002</v>
+      </c>
+      <c r="H30" s="14">
+        <v>4556.8150899648399</v>
+      </c>
+      <c r="I30" s="14">
+        <v>5905.8976607488103</v>
+      </c>
+      <c r="J30" s="14">
+        <v>7357.1529509849497</v>
+      </c>
+      <c r="K30" s="14">
+        <v>8728.7001431875997</v>
+      </c>
+      <c r="L30" s="14">
+        <v>10273.1676332716</v>
+      </c>
+      <c r="M30" s="14">
+        <v>12088.1509811791</v>
+      </c>
+    </row>
+    <row r="31" spans="4:13" x14ac:dyDescent="0.25">
+      <c r="D31" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="E29" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="F29" s="15">
-        <v>4026.4255253246401</v>
-      </c>
-      <c r="G29" s="15">
-        <v>4913.2020396430598</v>
-      </c>
-      <c r="H29" s="15">
-        <v>5687.6455111417899</v>
-      </c>
-      <c r="I29" s="15">
-        <v>7259.0370999061797</v>
-      </c>
-      <c r="J29" s="15">
-        <v>9264.5752121137193</v>
-      </c>
-      <c r="K29" s="15">
-        <v>11824.206527615201</v>
-      </c>
-      <c r="L29" s="15">
-        <v>15091.0167823875</v>
-      </c>
-      <c r="M29" s="15">
-        <v>18355.616359657</v>
-      </c>
-    </row>
-    <row r="30" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="D30" s="14" t="s">
+      <c r="E31" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="F31" s="14">
+        <v>27275.0772727328</v>
+      </c>
+      <c r="G31" s="14">
+        <v>25497.240202459601</v>
+      </c>
+      <c r="H31" s="14">
+        <v>32220.485987141801</v>
+      </c>
+      <c r="I31" s="14">
+        <v>38626.826487720296</v>
+      </c>
+      <c r="J31" s="14">
+        <v>45805.892951210597</v>
+      </c>
+      <c r="K31" s="14">
+        <v>52966.084365633898</v>
+      </c>
+      <c r="L31" s="14">
+        <v>61417.3146710086</v>
+      </c>
+      <c r="M31" s="14">
+        <v>72812.641111213699</v>
+      </c>
+    </row>
+    <row r="33" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="D33" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="E30" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="F30" s="15">
-        <v>6668.8297496027999</v>
-      </c>
-      <c r="G30" s="15">
-        <v>3770.2856351884002</v>
-      </c>
-      <c r="H30" s="15">
-        <v>4556.8150899648399</v>
-      </c>
-      <c r="I30" s="15">
-        <v>5905.8976607488103</v>
-      </c>
-      <c r="J30" s="15">
-        <v>7357.1529509849497</v>
-      </c>
-      <c r="K30" s="15">
-        <v>8728.7001431875997</v>
-      </c>
-      <c r="L30" s="15">
-        <v>10273.1676332716</v>
-      </c>
-      <c r="M30" s="15">
-        <v>12088.1509811791</v>
-      </c>
-    </row>
-    <row r="31" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="D31" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="E31" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="F31" s="15">
-        <v>27275.0772727328</v>
-      </c>
-      <c r="G31" s="15">
-        <v>25497.240202459601</v>
-      </c>
-      <c r="H31" s="15">
-        <v>32220.485987141801</v>
-      </c>
-      <c r="I31" s="15">
-        <v>38626.826487720296</v>
-      </c>
-      <c r="J31" s="15">
-        <v>45805.892951210597</v>
-      </c>
-      <c r="K31" s="15">
-        <v>52966.084365633898</v>
-      </c>
-      <c r="L31" s="15">
-        <v>61417.3146710086</v>
-      </c>
-      <c r="M31" s="15">
-        <v>72812.641111213699</v>
-      </c>
-    </row>
-    <row r="33" spans="4:10" x14ac:dyDescent="0.3">
-      <c r="D33" s="17" t="s">
+      <c r="E33" s="16" t="s">
         <v>32</v>
-      </c>
-      <c r="E33" s="17" t="s">
-        <v>33</v>
       </c>
       <c r="F33">
         <v>20.633521014270116</v>
@@ -1231,9 +1248,9 @@
         <v>29.390040974058223</v>
       </c>
     </row>
-    <row r="34" spans="4:10" x14ac:dyDescent="0.3">
-      <c r="E34" s="17" t="s">
-        <v>34</v>
+    <row r="34" spans="4:10" x14ac:dyDescent="0.25">
+      <c r="E34" s="16" t="s">
+        <v>33</v>
       </c>
       <c r="F34">
         <f>F33*10^3</f>
@@ -1256,7 +1273,7 @@
         <v>29390.040974058222</v>
       </c>
     </row>
-    <row r="35" spans="4:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="4:10" x14ac:dyDescent="0.25">
       <c r="F35">
         <v>20633.521014270114</v>
       </c>

--- a/SuppXLS/Scen_UC_CO2BND_CNDC.xlsx
+++ b/SuppXLS/Scen_UC_CO2BND_CNDC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="J:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261025_v01\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B639C1-BD97-400E-9F97-DF88ADF3B238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29EE379F-2B6B-4F79-A5C4-E20FF4195BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UC_CO2" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="35">
   <si>
     <t>~UC_Sets: R_E: AllRegions</t>
   </si>
@@ -135,6 +135,9 @@
   </si>
   <si>
     <t>ktCO2</t>
+  </si>
+  <si>
+    <t>UC_RHSRTS~0</t>
   </si>
 </sst>
 </file>
@@ -295,7 +298,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -328,6 +331,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="3" builtinId="3"/>
@@ -893,6 +897,9 @@
       <c r="L5" s="8" t="s">
         <v>13</v>
       </c>
+      <c r="M5" s="18" t="s">
+        <v>34</v>
+      </c>
       <c r="N5" s="4" t="s">
         <v>11</v>
       </c>
@@ -918,6 +925,9 @@
       </c>
       <c r="L6" s="17">
         <v>32850.09812767776</v>
+      </c>
+      <c r="M6">
+        <v>5</v>
       </c>
       <c r="N6" t="s">
         <v>16</v>
